--- a/research/traditional_assets/database/data/brazil/brazil_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0645</v>
+        <v>0.204</v>
       </c>
       <c r="E2">
-        <v>0.108</v>
+        <v>0.173</v>
       </c>
       <c r="F2">
-        <v>0.0663</v>
+        <v>0.062</v>
       </c>
       <c r="G2">
-        <v>0.2754546159513008</v>
+        <v>0.1806307540226052</v>
       </c>
       <c r="H2">
-        <v>0.2197181187235857</v>
+        <v>0.146806331360242</v>
       </c>
       <c r="I2">
-        <v>0.2368054747780234</v>
+        <v>0.1434203160916118</v>
       </c>
       <c r="J2">
-        <v>0.1702393620146365</v>
+        <v>0.1119458896253052</v>
       </c>
       <c r="K2">
-        <v>1959.96</v>
+        <v>2632.96</v>
       </c>
       <c r="L2">
-        <v>0.379969756891939</v>
+        <v>0.3135857461024499</v>
       </c>
       <c r="M2">
-        <v>1695.432</v>
+        <v>1585.381</v>
       </c>
       <c r="N2">
-        <v>0.04839335053547371</v>
+        <v>0.03912907517147251</v>
       </c>
       <c r="O2">
-        <v>0.8650339802853122</v>
+        <v>0.6021287828147788</v>
       </c>
       <c r="P2">
-        <v>1477.732</v>
+        <v>1011.641</v>
       </c>
       <c r="Q2">
-        <v>0.04217945790423128</v>
+        <v>0.02496849447264955</v>
       </c>
       <c r="R2">
-        <v>0.7539602849037738</v>
+        <v>0.384221940325717</v>
       </c>
       <c r="S2">
-        <v>217.7</v>
+        <v>573.74</v>
       </c>
       <c r="T2">
-        <v>0.128403852233531</v>
+        <v>0.3618940809811648</v>
       </c>
       <c r="U2">
-        <v>9213.4</v>
+        <v>11388.4</v>
       </c>
       <c r="V2">
-        <v>0.2629815267280159</v>
+        <v>0.2810791599513287</v>
       </c>
       <c r="W2">
-        <v>0.2138399504926221</v>
+        <v>0.1913979011070819</v>
       </c>
       <c r="X2">
-        <v>0.02980956859172251</v>
+        <v>0.0582031843177226</v>
       </c>
       <c r="Y2">
-        <v>0.1840303819008995</v>
+        <v>0.1331947167893593</v>
       </c>
       <c r="Z2">
-        <v>0.2911322675829621</v>
+        <v>0.2305949576759671</v>
       </c>
       <c r="AA2">
-        <v>-0.07766132792767122</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.02998146833574605</v>
+        <v>0.05853657124850558</v>
       </c>
       <c r="AC2">
-        <v>-0.1141046938453767</v>
+        <v>-0.07505707181507122</v>
       </c>
       <c r="AD2">
-        <v>35682.56400000001</v>
+        <v>43727.136</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>35682.56400000001</v>
+        <v>43727.136</v>
       </c>
       <c r="AG2">
-        <v>26469.164</v>
+        <v>32338.736</v>
       </c>
       <c r="AH2">
-        <v>0.5045828042052258</v>
+        <v>0.5190544267238734</v>
       </c>
       <c r="AI2">
-        <v>0.7524559764751253</v>
+        <v>0.7528292601564059</v>
       </c>
       <c r="AJ2">
-        <v>0.4303679702203925</v>
+        <v>0.4438754027908089</v>
       </c>
       <c r="AK2">
-        <v>0.6927638102783747</v>
+        <v>0.6925474527049126</v>
       </c>
       <c r="AL2">
-        <v>90.587</v>
+        <v>410.475</v>
       </c>
       <c r="AM2">
-        <v>-13.648</v>
+        <v>83.58500000000004</v>
       </c>
       <c r="AN2">
-        <v>31.89115244984744</v>
+        <v>39.88974274767378</v>
       </c>
       <c r="AO2">
-        <v>13.48416439444953</v>
+        <v>2.933674401607893</v>
       </c>
       <c r="AP2">
-        <v>23.65671212259337</v>
+        <v>29.50076263455573</v>
       </c>
       <c r="AQ2">
-        <v>-89.49956037514657</v>
+        <v>14.40689118861039</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B3 S.A. - Brasil, Bolsa, Balcão (BOVESPA:B3SA3)</t>
+          <t>Financeira Alfa S.A. - Crédito, Financiamento e Investimentos (BOVESPA:CRIV3)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,124 +725,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.334</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="E3">
-        <v>1.119</v>
-      </c>
-      <c r="F3">
-        <v>0.0663</v>
+        <v>-0.0122</v>
       </c>
       <c r="G3">
-        <v>0.773370780076804</v>
+        <v>0.3501189532117367</v>
       </c>
       <c r="H3">
-        <v>0.6085860033243538</v>
+        <v>0.3501189532117367</v>
       </c>
       <c r="I3">
-        <v>0.6568464492462888</v>
+        <v>0.7260111022997621</v>
       </c>
       <c r="J3">
-        <v>0.4648304007909632</v>
+        <v>0.5143865895017463</v>
       </c>
       <c r="K3">
-        <v>871</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="L3">
-        <v>0.4992262280048146</v>
+        <v>0.03917525773195877</v>
       </c>
       <c r="M3">
-        <v>1369.1</v>
+        <v>1.83</v>
       </c>
       <c r="N3">
-        <v>0.1128707810516249</v>
+        <v>0.01808300395256917</v>
       </c>
       <c r="O3">
-        <v>1.57187141216992</v>
+        <v>0.1852226720647773</v>
       </c>
       <c r="P3">
-        <v>1151.4</v>
+        <v>1.83</v>
       </c>
       <c r="Q3">
-        <v>0.09492324687958582</v>
+        <v>0.01808300395256917</v>
       </c>
       <c r="R3">
-        <v>1.321928817451206</v>
+        <v>0.1852226720647773</v>
       </c>
       <c r="S3">
-        <v>217.7</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.1590095683295596</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>696.5</v>
+        <v>658.3</v>
       </c>
       <c r="V3">
-        <v>0.05742056752790648</v>
+        <v>6.50494071146245</v>
       </c>
       <c r="W3">
-        <v>0.1959152458500157</v>
+        <v>0.05235824059353472</v>
       </c>
       <c r="X3">
-        <v>0.03076188491008217</v>
+        <v>0.05639058962150749</v>
       </c>
       <c r="Y3">
-        <v>0.1651533609399336</v>
+        <v>-0.004032349027972768</v>
       </c>
       <c r="Z3">
-        <v>1.141669938489726</v>
+        <v>1.996927803379416</v>
       </c>
       <c r="AA3">
-        <v>0.5306828950791737</v>
+        <v>1.027192882261552</v>
       </c>
       <c r="AB3">
-        <v>0.03103741317575371</v>
+        <v>0.05642465496817049</v>
       </c>
       <c r="AC3">
-        <v>0.49964548190342</v>
+        <v>0.9707682272933814</v>
       </c>
       <c r="AD3">
-        <v>2691.7</v>
+        <v>0.516</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2691.7</v>
+        <v>0.516</v>
       </c>
       <c r="AG3">
-        <v>1995.2</v>
+        <v>-657.784</v>
       </c>
       <c r="AH3">
-        <v>0.1816077994804844</v>
+        <v>0.005072948208738054</v>
       </c>
       <c r="AI3">
-        <v>0.3924962452062585</v>
+        <v>0.002579793616510679</v>
       </c>
       <c r="AJ3">
-        <v>0.1412530973451327</v>
+        <v>1.181823408506173</v>
       </c>
       <c r="AK3">
-        <v>0.3238225078715876</v>
+        <v>1.435319583489714</v>
       </c>
       <c r="AL3">
-        <v>50.5</v>
+        <v>164</v>
       </c>
       <c r="AM3">
-        <v>-52.7</v>
+        <v>164</v>
       </c>
       <c r="AN3">
-        <v>2.581471180588855</v>
+        <v>0.002810457516339869</v>
       </c>
       <c r="AO3">
-        <v>22.69306930693069</v>
+        <v>1.116463414634146</v>
       </c>
       <c r="AP3">
-        <v>1.913493814136376</v>
+        <v>-3.582701525054466</v>
       </c>
       <c r="AQ3">
-        <v>-21.74573055028463</v>
+        <v>1.116463414634146</v>
       </c>
     </row>
     <row r="4">
@@ -853,7 +850,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Banco BTG Pactual S.A. (BOVESPA:BPAC3)</t>
+          <t>B3 S.A. - Brasil, Bolsa, Balcão (BOVESPA:B3SA3)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -862,109 +859,124 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0645</v>
+        <v>0.224</v>
       </c>
       <c r="E4">
-        <v>0.064</v>
+        <v>0.204</v>
+      </c>
+      <c r="F4">
+        <v>0.062</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.8651047642050601</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.6936175351729968</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.6253245576957913</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>0.4602458032680659</v>
       </c>
       <c r="K4">
-        <v>1074.6</v>
+        <v>797</v>
       </c>
       <c r="L4">
-        <v>0.3293086540818828</v>
+        <v>0.4812511321780086</v>
       </c>
       <c r="M4">
-        <v>322</v>
+        <v>1314.7</v>
       </c>
       <c r="N4">
-        <v>0.01430513474370707</v>
+        <v>0.08929020164494463</v>
       </c>
       <c r="O4">
-        <v>0.2996463800483901</v>
+        <v>1.649560853199498</v>
       </c>
       <c r="P4">
-        <v>322</v>
+        <v>761.1</v>
       </c>
       <c r="Q4">
-        <v>0.01430513474370707</v>
+        <v>0.05169146761387948</v>
       </c>
       <c r="R4">
-        <v>0.2996463800483901</v>
+        <v>0.9549560853199498</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>553.6</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.4210846580969043</v>
       </c>
       <c r="U4">
-        <v>8356.5</v>
+        <v>788.5</v>
       </c>
       <c r="V4">
-        <v>0.3712449021297768</v>
+        <v>0.05355238761469448</v>
       </c>
       <c r="W4">
-        <v>0.2317646551352284</v>
+        <v>0.1913979011070819</v>
       </c>
       <c r="X4">
-        <v>0.04197481837893759</v>
+        <v>0.0582031843177226</v>
       </c>
       <c r="Y4">
-        <v>0.1897898367562908</v>
+        <v>0.1331947167893593</v>
       </c>
       <c r="Z4">
-        <v>0.1978800300773765</v>
+        <v>0.8170605357935762</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>0.3760486826149507</v>
       </c>
       <c r="AB4">
-        <v>0.04396120833967253</v>
+        <v>0.05853657124850558</v>
       </c>
       <c r="AC4">
-        <v>-0.04396120833967253</v>
+        <v>0.3175121113664451</v>
       </c>
       <c r="AD4">
-        <v>32988.3</v>
+        <v>2381.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>32988.3</v>
+        <v>2381.6</v>
       </c>
       <c r="AG4">
-        <v>24631.8</v>
+        <v>1593.1</v>
       </c>
       <c r="AH4">
-        <v>0.5944084169253862</v>
+        <v>0.1392300721990003</v>
       </c>
       <c r="AI4">
-        <v>0.8195708397617929</v>
+        <v>0.3868620252753322</v>
       </c>
       <c r="AJ4">
-        <v>0.5225110943293765</v>
+        <v>0.09763436906294048</v>
       </c>
       <c r="AK4">
-        <v>0.772297157476908</v>
+        <v>0.2967937850475995</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>246.1</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>-75.40000000000001</v>
+      </c>
+      <c r="AN4">
+        <v>2.570811744386874</v>
+      </c>
+      <c r="AO4">
+        <v>4.208045509955302</v>
+      </c>
+      <c r="AP4">
+        <v>1.719667530224525</v>
+      </c>
+      <c r="AQ4">
+        <v>-13.73474801061008</v>
       </c>
     </row>
     <row r="5">
@@ -975,7 +987,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Financeira Alfa S.A. - Crédito, Financiamento e Investimentos (BOVESPA:CRIV3)</t>
+          <t>Banco do Nordeste do Brasil S.A. (BOVESPA:BNBR3)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -984,46 +996,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.006939999999999999</v>
+        <v>0.184</v>
       </c>
       <c r="E5">
-        <v>0.108</v>
+        <v>0.142</v>
       </c>
       <c r="G5">
-        <v>0.4996326230712712</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>0.4996326230712712</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>0.56208670095518</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>0.3438325478038028</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>12.2</v>
+        <v>368.2</v>
       </c>
       <c r="L5">
-        <v>0.0896399706098457</v>
+        <v>0.2200968378265288</v>
       </c>
       <c r="M5">
-        <v>3.55</v>
+        <v>27</v>
       </c>
       <c r="N5">
-        <v>0.03809012875536481</v>
+        <v>0.0219619326500732</v>
       </c>
       <c r="O5">
-        <v>0.290983606557377</v>
+        <v>0.07332971211298207</v>
       </c>
       <c r="P5">
-        <v>3.55</v>
+        <v>27</v>
       </c>
       <c r="Q5">
-        <v>0.03809012875536481</v>
+        <v>0.0219619326500732</v>
       </c>
       <c r="R5">
-        <v>0.290983606557377</v>
+        <v>0.07332971211298207</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1032,73 +1044,61 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>63.4</v>
+        <v>22.4</v>
       </c>
       <c r="V5">
-        <v>0.6802575107296137</v>
+        <v>0.0182202700504311</v>
       </c>
       <c r="W5">
-        <v>0.07015526164462334</v>
+        <v>0.280127814972611</v>
       </c>
       <c r="X5">
-        <v>0.02885725227336285</v>
+        <v>0.0747504588188628</v>
       </c>
       <c r="Y5">
-        <v>0.04129800937126049</v>
+        <v>0.2053773561537482</v>
       </c>
       <c r="Z5">
-        <v>-0.4517392458842273</v>
+        <v>0.571228573379772</v>
       </c>
       <c r="AA5">
-        <v>-0.1553226558553424</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.02892552349573838</v>
+        <v>0.07505707181507122</v>
       </c>
       <c r="AC5">
-        <v>-0.1842481793510808</v>
+        <v>-0.07505707181507122</v>
       </c>
       <c r="AD5">
-        <v>0.994</v>
+        <v>1957</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.994</v>
+        <v>1957</v>
       </c>
       <c r="AG5">
-        <v>-62.406</v>
+        <v>1934.6</v>
       </c>
       <c r="AH5">
-        <v>0.01055268913094252</v>
+        <v>0.6141727341200101</v>
       </c>
       <c r="AI5">
-        <v>0.00512122991952353</v>
+        <v>0.5522009029345373</v>
       </c>
       <c r="AJ5">
-        <v>-2.026563616288887</v>
+        <v>0.611441213653603</v>
       </c>
       <c r="AK5">
-        <v>-0.4774970541876444</v>
+        <v>0.5493525670149931</v>
       </c>
       <c r="AL5">
-        <v>39.9</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>39.713</v>
-      </c>
-      <c r="AN5">
-        <v>0.01290909090909091</v>
-      </c>
-      <c r="AO5">
-        <v>1.917293233082707</v>
-      </c>
-      <c r="AP5">
-        <v>-0.8104675324675324</v>
-      </c>
-      <c r="AQ5">
-        <v>1.926321355727344</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1109,109 +1109,246 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>Banco BTG Pactual S.A. (BOVESPA:BPAC3)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.392</v>
+      </c>
+      <c r="E6">
+        <v>0.27</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>1467.3</v>
+      </c>
+      <c r="L6">
+        <v>0.3058467952058364</v>
+      </c>
+      <c r="M6">
+        <v>239.4</v>
+      </c>
+      <c r="N6">
+        <v>0.009834126143001503</v>
+      </c>
+      <c r="O6">
+        <v>0.1631568186464936</v>
+      </c>
+      <c r="P6">
+        <v>221.7</v>
+      </c>
+      <c r="Q6">
+        <v>0.009107041628669313</v>
+      </c>
+      <c r="R6">
+        <v>0.1510938458392967</v>
+      </c>
+      <c r="S6">
+        <v>17.69999999999999</v>
+      </c>
+      <c r="T6">
+        <v>0.07393483709273178</v>
+      </c>
+      <c r="U6">
+        <v>9886.6</v>
+      </c>
+      <c r="V6">
+        <v>0.4061239412088499</v>
+      </c>
+      <c r="W6">
+        <v>0.2194355960339181</v>
+      </c>
+      <c r="X6">
+        <v>0.07505262558842002</v>
+      </c>
+      <c r="Y6">
+        <v>0.1443829704454981</v>
+      </c>
+      <c r="Z6">
+        <v>0.153184220189345</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.07517441442671624</v>
+      </c>
+      <c r="AC6">
+        <v>-0.07517441442671624</v>
+      </c>
+      <c r="AD6">
+        <v>39387</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>39387</v>
+      </c>
+      <c r="AG6">
+        <v>29500.4</v>
+      </c>
+      <c r="AH6">
+        <v>0.6180214276299685</v>
+      </c>
+      <c r="AI6">
+        <v>0.8192534013357823</v>
+      </c>
+      <c r="AJ6">
+        <v>0.5478844518072513</v>
+      </c>
+      <c r="AK6">
+        <v>0.7724619731291616</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>TC Traders Club S.A. (BOVESPA:TRAD3)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="G6">
-        <v>0.25</v>
-      </c>
-      <c r="H6">
-        <v>0.25</v>
-      </c>
-      <c r="I6">
-        <v>-0.07112676056338028</v>
-      </c>
-      <c r="J6">
-        <v>-0.07112676056338028</v>
-      </c>
-      <c r="K6">
-        <v>2.16</v>
-      </c>
-      <c r="L6">
-        <v>0.152112676056338</v>
-      </c>
-      <c r="M6">
-        <v>0.782</v>
-      </c>
-      <c r="N6">
-        <v>0.002589403973509934</v>
-      </c>
-      <c r="O6">
-        <v>0.362037037037037</v>
-      </c>
-      <c r="P6">
-        <v>0.782</v>
-      </c>
-      <c r="Q6">
-        <v>0.002589403973509934</v>
-      </c>
-      <c r="R6">
-        <v>0.362037037037037</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>97</v>
-      </c>
-      <c r="V6">
-        <v>0.3211920529801324</v>
-      </c>
-      <c r="X6">
-        <v>0.02880796401344508</v>
-      </c>
-      <c r="AB6">
-        <v>0.02885207772831529</v>
-      </c>
-      <c r="AD6">
-        <v>1.57</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>1.57</v>
-      </c>
-      <c r="AG6">
-        <v>-95.43000000000001</v>
-      </c>
-      <c r="AH6">
-        <v>0.005171789043713147</v>
-      </c>
-      <c r="AI6">
-        <v>0.01321882630293845</v>
-      </c>
-      <c r="AJ6">
-        <v>-0.4619741491988189</v>
-      </c>
-      <c r="AK6">
-        <v>-4.383555351401012</v>
-      </c>
-      <c r="AL6">
-        <v>0.187</v>
-      </c>
-      <c r="AM6">
-        <v>-0.661</v>
-      </c>
-      <c r="AN6">
-        <v>-1.928746928746929</v>
-      </c>
-      <c r="AO6">
-        <v>-5.401069518716578</v>
-      </c>
-      <c r="AP6">
-        <v>117.2358722358723</v>
-      </c>
-      <c r="AQ6">
-        <v>1.527987897125567</v>
+      <c r="G7">
+        <v>-0.2482954545454545</v>
+      </c>
+      <c r="H7">
+        <v>-0.2482954545454545</v>
+      </c>
+      <c r="I7">
+        <v>-0.8238636363636362</v>
+      </c>
+      <c r="J7">
+        <v>-0.8238636363636362</v>
+      </c>
+      <c r="K7">
+        <v>-9.42</v>
+      </c>
+      <c r="L7">
+        <v>-0.5352272727272727</v>
+      </c>
+      <c r="M7">
+        <v>2.451</v>
+      </c>
+      <c r="N7">
+        <v>0.02070101351351351</v>
+      </c>
+      <c r="O7">
+        <v>-0.2601910828025478</v>
+      </c>
+      <c r="P7">
+        <v>0.011</v>
+      </c>
+      <c r="Q7">
+        <v>9.290540540540539e-05</v>
+      </c>
+      <c r="R7">
+        <v>-0.001167728237791932</v>
+      </c>
+      <c r="S7">
+        <v>2.44</v>
+      </c>
+      <c r="T7">
+        <v>0.9955120359037127</v>
+      </c>
+      <c r="U7">
+        <v>32.6</v>
+      </c>
+      <c r="V7">
+        <v>0.2753378378378378</v>
+      </c>
+      <c r="W7">
+        <v>-0.0803754266211604</v>
+      </c>
+      <c r="X7">
+        <v>0.05643127331854358</v>
+      </c>
+      <c r="Y7">
+        <v>-0.136806699939704</v>
+      </c>
+      <c r="Z7">
+        <v>1.575649059982096</v>
+      </c>
+      <c r="AA7">
+        <v>-1.298119964189794</v>
+      </c>
+      <c r="AB7">
+        <v>0.05655198227056123</v>
+      </c>
+      <c r="AC7">
+        <v>-1.354671946460356</v>
+      </c>
+      <c r="AD7">
+        <v>1.02</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>1.02</v>
+      </c>
+      <c r="AG7">
+        <v>-31.58</v>
+      </c>
+      <c r="AH7">
+        <v>0.008541282867191425</v>
+      </c>
+      <c r="AI7">
+        <v>0.009548773637895526</v>
+      </c>
+      <c r="AJ7">
+        <v>-0.363741073485372</v>
+      </c>
+      <c r="AK7">
+        <v>-0.4254917811910536</v>
+      </c>
+      <c r="AL7">
+        <v>0.375</v>
+      </c>
+      <c r="AM7">
+        <v>-5.015</v>
+      </c>
+      <c r="AN7">
+        <v>-0.07391304347826087</v>
+      </c>
+      <c r="AO7">
+        <v>-38.66666666666666</v>
+      </c>
+      <c r="AP7">
+        <v>2.288405797101449</v>
+      </c>
+      <c r="AQ7">
+        <v>2.891326021934197</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/brazil/brazil_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.204</v>
+        <v>0.178</v>
       </c>
       <c r="E2">
-        <v>0.173</v>
+        <v>0.1525</v>
       </c>
       <c r="F2">
-        <v>0.062</v>
+        <v>0.102</v>
       </c>
       <c r="G2">
-        <v>0.1806307540226052</v>
+        <v>0.3626742538779301</v>
       </c>
       <c r="H2">
-        <v>0.146806331360242</v>
+        <v>0.3145895088550533</v>
       </c>
       <c r="I2">
-        <v>0.1434203160916118</v>
+        <v>0.3165081368078952</v>
       </c>
       <c r="J2">
-        <v>0.1119458896253052</v>
+        <v>0.2612455149536362</v>
       </c>
       <c r="K2">
-        <v>2632.96</v>
+        <v>2051.33</v>
       </c>
       <c r="L2">
-        <v>0.3135857461024499</v>
+        <v>0.2035025376682024</v>
       </c>
       <c r="M2">
-        <v>1585.381</v>
+        <v>1313.959</v>
       </c>
       <c r="N2">
-        <v>0.03912907517147251</v>
+        <v>0.0499347863264104</v>
       </c>
       <c r="O2">
-        <v>0.6021287828147788</v>
+        <v>0.6405400398765679</v>
       </c>
       <c r="P2">
-        <v>1011.641</v>
+        <v>755.669</v>
       </c>
       <c r="Q2">
-        <v>0.02496849447264955</v>
+        <v>0.02871792045907994</v>
       </c>
       <c r="R2">
-        <v>0.384221940325717</v>
+        <v>0.3683800266168779</v>
       </c>
       <c r="S2">
-        <v>573.74</v>
+        <v>558.2900000000001</v>
       </c>
       <c r="T2">
-        <v>0.3618940809811648</v>
+        <v>0.4248914920480776</v>
       </c>
       <c r="U2">
-        <v>11388.4</v>
+        <v>2766.6</v>
       </c>
       <c r="V2">
-        <v>0.2810791599513287</v>
+        <v>0.1051399471754043</v>
       </c>
       <c r="W2">
-        <v>0.1913979011070819</v>
+        <v>0.1930690600847669</v>
       </c>
       <c r="X2">
-        <v>0.0582031843177226</v>
+        <v>0.06160090921034564</v>
       </c>
       <c r="Y2">
-        <v>0.1331947167893593</v>
+        <v>0.1314681508744212</v>
       </c>
       <c r="Z2">
-        <v>0.2305949576759671</v>
+        <v>1.007786255878683</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>0.2810819087369886</v>
       </c>
       <c r="AB2">
-        <v>0.05853657124850558</v>
+        <v>0.06108591281299058</v>
       </c>
       <c r="AC2">
-        <v>-0.07505707181507122</v>
+        <v>0.219995995923998</v>
       </c>
       <c r="AD2">
-        <v>43727.136</v>
+        <v>6002.445</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>43727.136</v>
+        <v>6002.445</v>
       </c>
       <c r="AG2">
-        <v>32338.736</v>
+        <v>3235.845</v>
       </c>
       <c r="AH2">
-        <v>0.5190544267238734</v>
+        <v>0.1857425181284347</v>
       </c>
       <c r="AI2">
-        <v>0.7528292601564059</v>
+        <v>0.3275309397482149</v>
       </c>
       <c r="AJ2">
-        <v>0.4438754027908089</v>
+        <v>0.1095064882148826</v>
       </c>
       <c r="AK2">
-        <v>0.6925474527049126</v>
+        <v>0.2079625983587777</v>
       </c>
       <c r="AL2">
-        <v>410.475</v>
+        <v>1333.39</v>
       </c>
       <c r="AM2">
-        <v>83.58500000000004</v>
+        <v>1063.2</v>
       </c>
       <c r="AN2">
-        <v>39.88974274767378</v>
+        <v>1.76469835949903</v>
       </c>
       <c r="AO2">
-        <v>2.933674401607893</v>
+        <v>2.392728309046865</v>
       </c>
       <c r="AP2">
-        <v>29.50076263455573</v>
+        <v>0.9513273946022225</v>
       </c>
       <c r="AQ2">
-        <v>14.40689118861039</v>
+        <v>3.00079006772009</v>
       </c>
     </row>
     <row r="3">
@@ -725,46 +725,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.09279999999999999</v>
+        <v>0.228</v>
       </c>
       <c r="E3">
-        <v>-0.0122</v>
+        <v>-0.135</v>
       </c>
       <c r="G3">
-        <v>0.3501189532117367</v>
+        <v>0.538423277791594</v>
       </c>
       <c r="H3">
-        <v>0.3501189532117367</v>
+        <v>0.538423277791594</v>
       </c>
       <c r="I3">
-        <v>0.7260111022997621</v>
+        <v>0.7913454364585923</v>
       </c>
       <c r="J3">
-        <v>0.5143865895017463</v>
+        <v>0.789696800132637</v>
       </c>
       <c r="K3">
-        <v>9.880000000000001</v>
+        <v>6.29</v>
       </c>
       <c r="L3">
-        <v>0.03917525773195877</v>
+        <v>0.01564287490673962</v>
       </c>
       <c r="M3">
-        <v>1.83</v>
+        <v>4.2</v>
       </c>
       <c r="N3">
-        <v>0.01808300395256917</v>
+        <v>0.03422982885085574</v>
       </c>
       <c r="O3">
-        <v>0.1852226720647773</v>
+        <v>0.6677265500794913</v>
       </c>
       <c r="P3">
-        <v>1.83</v>
+        <v>4.2</v>
       </c>
       <c r="Q3">
-        <v>0.01808300395256917</v>
+        <v>0.03422982885085574</v>
       </c>
       <c r="R3">
-        <v>0.1852226720647773</v>
+        <v>0.6677265500794913</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -773,73 +773,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>658.3</v>
+        <v>1415.9</v>
       </c>
       <c r="V3">
-        <v>6.50494071146245</v>
+        <v>11.53952730236349</v>
       </c>
       <c r="W3">
-        <v>0.05235824059353472</v>
+        <v>0.03225641025641025</v>
       </c>
       <c r="X3">
-        <v>0.05639058962150749</v>
+        <v>0.06039287425348693</v>
       </c>
       <c r="Y3">
-        <v>-0.004032349027972768</v>
-      </c>
-      <c r="Z3">
-        <v>1.996927803379416</v>
-      </c>
-      <c r="AA3">
-        <v>1.027192882261552</v>
+        <v>-0.02813646399707668</v>
       </c>
       <c r="AB3">
-        <v>0.05642465496817049</v>
-      </c>
-      <c r="AC3">
-        <v>0.9707682272933814</v>
+        <v>0.06038408450443573</v>
       </c>
       <c r="AD3">
-        <v>0.516</v>
+        <v>0.315</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.516</v>
+        <v>0.315</v>
       </c>
       <c r="AG3">
-        <v>-657.784</v>
+        <v>-1415.585</v>
       </c>
       <c r="AH3">
-        <v>0.005072948208738054</v>
+        <v>0.002560663333739788</v>
       </c>
       <c r="AI3">
-        <v>0.002579793616510679</v>
+        <v>0.001438257653585371</v>
       </c>
       <c r="AJ3">
-        <v>1.181823408506173</v>
+        <v>1.094904032454549</v>
       </c>
       <c r="AK3">
-        <v>1.435319583489714</v>
+        <v>1.182724321885561</v>
       </c>
       <c r="AL3">
-        <v>164</v>
+        <v>310</v>
       </c>
       <c r="AM3">
-        <v>164</v>
+        <v>310</v>
       </c>
       <c r="AN3">
-        <v>0.002810457516339869</v>
+        <v>0.0009880803011292345</v>
       </c>
       <c r="AO3">
-        <v>1.116463414634146</v>
+        <v>1.026451612903226</v>
       </c>
       <c r="AP3">
-        <v>-3.582701525054466</v>
+        <v>-4.440354454203262</v>
       </c>
       <c r="AQ3">
-        <v>1.116463414634146</v>
+        <v>1.026451612903226</v>
       </c>
     </row>
     <row r="4">
@@ -850,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B3 S.A. - Brasil, Bolsa, Balcão (BOVESPA:B3SA3)</t>
+          <t>Aesapar Fundo de Investimento Imobiliário - FII (BOVESPA:RBED11)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,124 +850,88 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.224</v>
+        <v>0.246</v>
       </c>
       <c r="E4">
-        <v>0.204</v>
-      </c>
-      <c r="F4">
-        <v>0.062</v>
+        <v>0.105</v>
       </c>
       <c r="G4">
-        <v>0.8651047642050601</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>0.6936175351729968</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0.6253245576957913</v>
+        <v>0.7946428571428572</v>
       </c>
       <c r="J4">
-        <v>0.4602458032680659</v>
+        <v>0.7946428571428572</v>
       </c>
       <c r="K4">
-        <v>797</v>
+        <v>6.64</v>
       </c>
       <c r="L4">
-        <v>0.4812511321780086</v>
+        <v>0.9880952380952381</v>
       </c>
       <c r="M4">
-        <v>1314.7</v>
+        <v>5.42</v>
       </c>
       <c r="N4">
-        <v>0.08929020164494463</v>
+        <v>0.07569832402234637</v>
       </c>
       <c r="O4">
-        <v>1.649560853199498</v>
+        <v>0.8162650602409639</v>
       </c>
       <c r="P4">
-        <v>761.1</v>
+        <v>5.42</v>
       </c>
       <c r="Q4">
-        <v>0.05169146761387948</v>
+        <v>0.07569832402234637</v>
       </c>
       <c r="R4">
-        <v>0.9549560853199498</v>
+        <v>0.8162650602409639</v>
       </c>
       <c r="S4">
-        <v>553.6</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.4210846580969043</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>788.5</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>0.05355238761469448</v>
-      </c>
-      <c r="W4">
-        <v>0.1913979011070819</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>0.0582031843177226</v>
-      </c>
-      <c r="Y4">
-        <v>0.1331947167893593</v>
-      </c>
-      <c r="Z4">
-        <v>0.8170605357935762</v>
-      </c>
-      <c r="AA4">
-        <v>0.3760486826149507</v>
+        <v>0.06035634968055631</v>
       </c>
       <c r="AB4">
-        <v>0.05853657124850558</v>
-      </c>
-      <c r="AC4">
-        <v>0.3175121113664451</v>
+        <v>0.06035634968055631</v>
       </c>
       <c r="AD4">
-        <v>2381.6</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2381.6</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>1593.1</v>
+        <v>0</v>
       </c>
       <c r="AH4">
-        <v>0.1392300721990003</v>
-      </c>
-      <c r="AI4">
-        <v>0.3868620252753322</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>0.09763436906294048</v>
-      </c>
-      <c r="AK4">
-        <v>0.2967937850475995</v>
+        <v>0</v>
       </c>
       <c r="AL4">
-        <v>246.1</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>-75.40000000000001</v>
-      </c>
-      <c r="AN4">
-        <v>2.570811744386874</v>
-      </c>
-      <c r="AO4">
-        <v>4.208045509955302</v>
-      </c>
-      <c r="AP4">
-        <v>1.719667530224525</v>
-      </c>
-      <c r="AQ4">
-        <v>-13.73474801061008</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -987,7 +942,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Banco do Nordeste do Brasil S.A. (BOVESPA:BNBR3)</t>
+          <t>B3 S.A. - Brasil, Bolsa, Balcão (BOVESPA:B3SA3)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -996,109 +951,124 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.184</v>
+        <v>0.146</v>
       </c>
       <c r="E5">
-        <v>0.142</v>
+        <v>0.159</v>
+      </c>
+      <c r="F5">
+        <v>0.0218</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.7777037530535198</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>0.6049300466355763</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>0.6076504552520542</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>0.4465826591299339</v>
       </c>
       <c r="K5">
-        <v>368.2</v>
+        <v>845</v>
       </c>
       <c r="L5">
-        <v>0.2200968378265288</v>
+        <v>0.4691316899844548</v>
       </c>
       <c r="M5">
-        <v>27</v>
+        <v>884.7</v>
       </c>
       <c r="N5">
-        <v>0.0219619326500732</v>
+        <v>0.05203566681174935</v>
       </c>
       <c r="O5">
-        <v>0.07332971211298207</v>
+        <v>1.04698224852071</v>
       </c>
       <c r="P5">
-        <v>27</v>
+        <v>404.1</v>
       </c>
       <c r="Q5">
-        <v>0.0219619326500732</v>
+        <v>0.02376807161594655</v>
       </c>
       <c r="R5">
-        <v>0.07332971211298207</v>
+        <v>0.478224852071006</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>480.6</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.54323499491353</v>
       </c>
       <c r="U5">
-        <v>22.4</v>
+        <v>635.7</v>
       </c>
       <c r="V5">
-        <v>0.0182202700504311</v>
+        <v>0.03739015868907999</v>
       </c>
       <c r="W5">
-        <v>0.280127814972611</v>
+        <v>0.223995334535044</v>
       </c>
       <c r="X5">
-        <v>0.0747504588188628</v>
+        <v>0.06238493229599108</v>
       </c>
       <c r="Y5">
-        <v>0.2053773561537482</v>
+        <v>0.1616104022390529</v>
       </c>
       <c r="Z5">
-        <v>0.571228573379772</v>
+        <v>1.825663896209203</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>0.8153098374466213</v>
       </c>
       <c r="AB5">
-        <v>0.07505707181507122</v>
+        <v>0.06148815496000443</v>
       </c>
       <c r="AC5">
-        <v>-0.07505707181507122</v>
+        <v>0.7538216824866169</v>
       </c>
       <c r="AD5">
-        <v>1957</v>
+        <v>2424.2</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1957</v>
+        <v>2424.2</v>
       </c>
       <c r="AG5">
-        <v>1934.6</v>
+        <v>1788.5</v>
       </c>
       <c r="AH5">
-        <v>0.6141727341200101</v>
+        <v>0.1247915165242458</v>
       </c>
       <c r="AI5">
-        <v>0.5522009029345373</v>
+        <v>0.3742088851841561</v>
       </c>
       <c r="AJ5">
-        <v>0.611441213653603</v>
+        <v>0.09518208863083612</v>
       </c>
       <c r="AK5">
-        <v>0.5493525670149931</v>
+        <v>0.3061189559264013</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>139.4</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>-27.79999999999998</v>
+      </c>
+      <c r="AN5">
+        <v>2.460866917064257</v>
+      </c>
+      <c r="AO5">
+        <v>7.851506456241033</v>
+      </c>
+      <c r="AP5">
+        <v>1.815551720637498</v>
+      </c>
+      <c r="AQ5">
+        <v>-39.37050359712233</v>
       </c>
     </row>
     <row r="6">
@@ -1109,7 +1079,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Banco BTG Pactual S.A. (BOVESPA:BPAC3)</t>
+          <t>PagSeguro Digital Ltd. (NYSE:PAGS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1118,109 +1088,124 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.392</v>
+        <v>0.332</v>
       </c>
       <c r="E6">
-        <v>0.27</v>
+        <v>0.146</v>
+      </c>
+      <c r="F6">
+        <v>0.102</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>0.4379378890083749</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>0.38139928960146</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>0.3452927949946231</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>0.2846564522986294</v>
       </c>
       <c r="K6">
-        <v>1467.3</v>
+        <v>315</v>
       </c>
       <c r="L6">
-        <v>0.3058467952058364</v>
+        <v>0.1026493303353212</v>
       </c>
       <c r="M6">
-        <v>239.4</v>
+        <v>69.8</v>
       </c>
       <c r="N6">
-        <v>0.009834126143001503</v>
+        <v>0.01750689741660396</v>
       </c>
       <c r="O6">
-        <v>0.1631568186464936</v>
+        <v>0.2215873015873016</v>
       </c>
       <c r="P6">
-        <v>221.7</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.009107041628669313</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.1510938458392967</v>
+        <v>-0</v>
       </c>
       <c r="S6">
-        <v>17.69999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="T6">
-        <v>0.07393483709273178</v>
+        <v>1</v>
       </c>
       <c r="U6">
-        <v>9886.6</v>
+        <v>395.4</v>
       </c>
       <c r="V6">
-        <v>0.4061239412088499</v>
+        <v>0.09917231000752445</v>
       </c>
       <c r="W6">
-        <v>0.2194355960339181</v>
+        <v>0.148102872725563</v>
       </c>
       <c r="X6">
-        <v>0.07505262558842002</v>
+        <v>0.06058508379883713</v>
       </c>
       <c r="Y6">
-        <v>0.1443829704454981</v>
+        <v>0.0875177889267259</v>
       </c>
       <c r="Z6">
-        <v>0.153184220189345</v>
+        <v>1.496269930274513</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>0.4259228900330606</v>
       </c>
       <c r="AB6">
-        <v>0.07517441442671624</v>
+        <v>0.06049985622887433</v>
       </c>
       <c r="AC6">
-        <v>-0.07517441442671624</v>
+        <v>0.3654230338041862</v>
       </c>
       <c r="AD6">
-        <v>39387</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>39387</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AG6">
-        <v>29500.4</v>
+        <v>-331.3</v>
       </c>
       <c r="AH6">
-        <v>0.6180214276299685</v>
+        <v>0.01582286292611883</v>
       </c>
       <c r="AI6">
-        <v>0.8192534013357823</v>
+        <v>0.0242729475916389</v>
       </c>
       <c r="AJ6">
-        <v>0.5478844518072513</v>
+        <v>-0.09062559838061109</v>
       </c>
       <c r="AK6">
-        <v>0.7724619731291616</v>
+        <v>-0.147546094237107</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>472.5</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>472.5</v>
+      </c>
+      <c r="AN6">
+        <v>0.04882321578185695</v>
+      </c>
+      <c r="AO6">
+        <v>2.242539682539682</v>
+      </c>
+      <c r="AP6">
+        <v>-0.2523421433467895</v>
+      </c>
+      <c r="AQ6">
+        <v>2.242539682539682</v>
       </c>
     </row>
     <row r="7">
@@ -1231,124 +1216,648 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>CSU Digital S.A. (BOVESPA:CSUD3)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.0387</v>
+      </c>
+      <c r="E7">
+        <v>0.163</v>
+      </c>
+      <c r="G7">
+        <v>0.1968134957825679</v>
+      </c>
+      <c r="H7">
+        <v>0.1968134957825679</v>
+      </c>
+      <c r="I7">
+        <v>0.2155576382380506</v>
+      </c>
+      <c r="J7">
+        <v>0.1644342337709731</v>
+      </c>
+      <c r="K7">
+        <v>17.3</v>
+      </c>
+      <c r="L7">
+        <v>0.162136832239925</v>
+      </c>
+      <c r="M7">
+        <v>3.36</v>
+      </c>
+      <c r="N7">
+        <v>0.0201318154583583</v>
+      </c>
+      <c r="O7">
+        <v>0.1942196531791907</v>
+      </c>
+      <c r="P7">
+        <v>3.36</v>
+      </c>
+      <c r="Q7">
+        <v>0.0201318154583583</v>
+      </c>
+      <c r="R7">
+        <v>0.1942196531791907</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>15.9</v>
+      </c>
+      <c r="V7">
+        <v>0.09526662672258837</v>
+      </c>
+      <c r="W7">
+        <v>0.2582089552238806</v>
+      </c>
+      <c r="X7">
+        <v>0.06160090921034564</v>
+      </c>
+      <c r="Y7">
+        <v>0.196608046013535</v>
+      </c>
+      <c r="Z7">
+        <v>1.709388016661326</v>
+      </c>
+      <c r="AA7">
+        <v>0.2810819087369886</v>
+      </c>
+      <c r="AB7">
+        <v>0.06108591281299058</v>
+      </c>
+      <c r="AC7">
+        <v>0.219995995923998</v>
+      </c>
+      <c r="AD7">
+        <v>14.6</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>14.6</v>
+      </c>
+      <c r="AG7">
+        <v>-1.300000000000001</v>
+      </c>
+      <c r="AH7">
+        <v>0.08044077134986226</v>
+      </c>
+      <c r="AI7">
+        <v>0.1502057613168724</v>
+      </c>
+      <c r="AJ7">
+        <v>-0.007850241545893725</v>
+      </c>
+      <c r="AK7">
+        <v>-0.01599015990159902</v>
+      </c>
+      <c r="AL7">
+        <v>2.09</v>
+      </c>
+      <c r="AM7">
+        <v>0.2599999999999998</v>
+      </c>
+      <c r="AN7">
+        <v>0.6160337552742616</v>
+      </c>
+      <c r="AO7">
+        <v>11.00478468899522</v>
+      </c>
+      <c r="AP7">
+        <v>-0.05485232067510552</v>
+      </c>
+      <c r="AQ7">
+        <v>88.46153846153854</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Valid Soluções S.A. (BOVESPA:VLID3)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.0434</v>
+      </c>
+      <c r="E8">
+        <v>0.284</v>
+      </c>
+      <c r="G8">
+        <v>0.1875445685761826</v>
+      </c>
+      <c r="H8">
+        <v>0.1875445685761826</v>
+      </c>
+      <c r="I8">
+        <v>0.2079866888519135</v>
+      </c>
+      <c r="J8">
+        <v>0.1569637370923617</v>
+      </c>
+      <c r="K8">
+        <v>40.5</v>
+      </c>
+      <c r="L8">
+        <v>0.09626812455431424</v>
+      </c>
+      <c r="M8">
+        <v>6.52</v>
+      </c>
+      <c r="N8">
+        <v>0.01920471281296024</v>
+      </c>
+      <c r="O8">
+        <v>0.1609876543209876</v>
+      </c>
+      <c r="P8">
+        <v>4.81</v>
+      </c>
+      <c r="Q8">
+        <v>0.01416789396170839</v>
+      </c>
+      <c r="R8">
+        <v>0.1187654320987654</v>
+      </c>
+      <c r="S8">
+        <v>1.71</v>
+      </c>
+      <c r="T8">
+        <v>0.2622699386503067</v>
+      </c>
+      <c r="U8">
+        <v>87</v>
+      </c>
+      <c r="V8">
+        <v>0.2562592047128129</v>
+      </c>
+      <c r="W8">
+        <v>0.1721206969825754</v>
+      </c>
+      <c r="X8">
+        <v>0.06653752977305161</v>
+      </c>
+      <c r="Y8">
+        <v>0.1055831672095238</v>
+      </c>
+      <c r="Z8">
+        <v>1.463304347826087</v>
+      </c>
+      <c r="AA8">
+        <v>0.2296857189382837</v>
+      </c>
+      <c r="AB8">
+        <v>0.06310329308709638</v>
+      </c>
+      <c r="AC8">
+        <v>0.1665824258511873</v>
+      </c>
+      <c r="AD8">
+        <v>147.5</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>147.5</v>
+      </c>
+      <c r="AG8">
+        <v>60.5</v>
+      </c>
+      <c r="AH8">
+        <v>0.3028747433264887</v>
+      </c>
+      <c r="AI8">
+        <v>0.3458382180539273</v>
+      </c>
+      <c r="AJ8">
+        <v>0.15125</v>
+      </c>
+      <c r="AK8">
+        <v>0.1782032400589102</v>
+      </c>
+      <c r="AL8">
+        <v>25.1</v>
+      </c>
+      <c r="AM8">
+        <v>12.7</v>
+      </c>
+      <c r="AN8">
+        <v>1.709154113557358</v>
+      </c>
+      <c r="AO8">
+        <v>3.48605577689243</v>
+      </c>
+      <c r="AP8">
+        <v>0.7010428736964079</v>
+      </c>
+      <c r="AQ8">
+        <v>6.889763779527558</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cielo S.A. (BOVESPA:CIEL3)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>-0.02</v>
+      </c>
+      <c r="E9">
+        <v>-0.108</v>
+      </c>
+      <c r="F9">
+        <v>0.113</v>
+      </c>
+      <c r="G9">
+        <v>0.2880396319886765</v>
+      </c>
+      <c r="H9">
+        <v>0.2880396319886765</v>
+      </c>
+      <c r="I9">
+        <v>0.2914838405284265</v>
+      </c>
+      <c r="J9">
+        <v>0.2137486542641466</v>
+      </c>
+      <c r="K9">
+        <v>387.2</v>
+      </c>
+      <c r="L9">
+        <v>0.1826845954234489</v>
+      </c>
+      <c r="M9">
+        <v>234.78</v>
+      </c>
+      <c r="N9">
+        <v>0.08980606663351566</v>
+      </c>
+      <c r="O9">
+        <v>0.606353305785124</v>
+      </c>
+      <c r="P9">
+        <v>228.6</v>
+      </c>
+      <c r="Q9">
+        <v>0.08744214512489001</v>
+      </c>
+      <c r="R9">
+        <v>0.5903925619834711</v>
+      </c>
+      <c r="S9">
+        <v>6.180000000000007</v>
+      </c>
+      <c r="T9">
+        <v>0.02632251469460775</v>
+      </c>
+      <c r="U9">
+        <v>171.8</v>
+      </c>
+      <c r="V9">
+        <v>0.06571548789350878</v>
+      </c>
+      <c r="W9">
+        <v>0.1930690600847669</v>
+      </c>
+      <c r="X9">
+        <v>0.06737987889774605</v>
+      </c>
+      <c r="Y9">
+        <v>0.1256891811870208</v>
+      </c>
+      <c r="Z9">
+        <v>0.6980765430472301</v>
+      </c>
+      <c r="AA9">
+        <v>0.1492129216497131</v>
+      </c>
+      <c r="AB9">
+        <v>0.0633539132165987</v>
+      </c>
+      <c r="AC9">
+        <v>0.08585900843311436</v>
+      </c>
+      <c r="AD9">
+        <v>1290.6</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>1290.6</v>
+      </c>
+      <c r="AG9">
+        <v>1118.8</v>
+      </c>
+      <c r="AH9">
+        <v>0.3305078235038029</v>
+      </c>
+      <c r="AI9">
+        <v>0.3035206133439947</v>
+      </c>
+      <c r="AJ9">
+        <v>0.2996973025099783</v>
+      </c>
+      <c r="AK9">
+        <v>0.2741955248388598</v>
+      </c>
+      <c r="AL9">
+        <v>384.3</v>
+      </c>
+      <c r="AM9">
+        <v>299.5</v>
+      </c>
+      <c r="AN9">
+        <v>1.87097709481009</v>
+      </c>
+      <c r="AO9">
+        <v>1.60759823054905</v>
+      </c>
+      <c r="AP9">
+        <v>1.621919396926645</v>
+      </c>
+      <c r="AQ9">
+        <v>2.062771285475793</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Banco do Nordeste do Brasil S.A. (BOVESPA:BNBR3)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>0.21</v>
+      </c>
+      <c r="E10">
+        <v>0.266</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>452.3</v>
+      </c>
+      <c r="L10">
+        <v>0.2110395670026129</v>
+      </c>
+      <c r="M10">
+        <v>104.9</v>
+      </c>
+      <c r="N10">
+        <v>0.05353679697866694</v>
+      </c>
+      <c r="O10">
+        <v>0.2319257130223303</v>
+      </c>
+      <c r="P10">
+        <v>104.9</v>
+      </c>
+      <c r="Q10">
+        <v>0.05353679697866694</v>
+      </c>
+      <c r="R10">
+        <v>0.2319257130223303</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>26.1</v>
+      </c>
+      <c r="V10">
+        <v>0.01332040420536899</v>
+      </c>
+      <c r="W10">
+        <v>0.2850031505986138</v>
+      </c>
+      <c r="X10">
+        <v>0.07532053131646249</v>
+      </c>
+      <c r="Y10">
+        <v>0.2096826192821513</v>
+      </c>
+      <c r="Z10">
+        <v>0.6085870059064061</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0.06839705797808907</v>
+      </c>
+      <c r="AC10">
+        <v>-0.06839705797808907</v>
+      </c>
+      <c r="AD10">
+        <v>2060.9</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>2060.9</v>
+      </c>
+      <c r="AG10">
+        <v>2034.8</v>
+      </c>
+      <c r="AH10">
+        <v>0.5126234360619855</v>
+      </c>
+      <c r="AI10">
+        <v>0.5006194281827677</v>
+      </c>
+      <c r="AJ10">
+        <v>0.5094386860948376</v>
+      </c>
+      <c r="AK10">
+        <v>0.4974331393927541</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>TC Traders Club S.A. (BOVESPA:TRAD3)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="G7">
-        <v>-0.2482954545454545</v>
-      </c>
-      <c r="H7">
-        <v>-0.2482954545454545</v>
-      </c>
-      <c r="I7">
-        <v>-0.8238636363636362</v>
-      </c>
-      <c r="J7">
-        <v>-0.8238636363636362</v>
-      </c>
-      <c r="K7">
-        <v>-9.42</v>
-      </c>
-      <c r="L7">
-        <v>-0.5352272727272727</v>
-      </c>
-      <c r="M7">
-        <v>2.451</v>
-      </c>
-      <c r="N7">
-        <v>0.02070101351351351</v>
-      </c>
-      <c r="O7">
-        <v>-0.2601910828025478</v>
-      </c>
-      <c r="P7">
-        <v>0.011</v>
-      </c>
-      <c r="Q7">
-        <v>9.290540540540539e-05</v>
-      </c>
-      <c r="R7">
-        <v>-0.001167728237791932</v>
-      </c>
-      <c r="S7">
-        <v>2.44</v>
-      </c>
-      <c r="T7">
-        <v>0.9955120359037127</v>
-      </c>
-      <c r="U7">
-        <v>32.6</v>
-      </c>
-      <c r="V7">
-        <v>0.2753378378378378</v>
-      </c>
-      <c r="W7">
-        <v>-0.0803754266211604</v>
-      </c>
-      <c r="X7">
-        <v>0.05643127331854358</v>
-      </c>
-      <c r="Y7">
-        <v>-0.136806699939704</v>
-      </c>
-      <c r="Z7">
-        <v>1.575649059982096</v>
-      </c>
-      <c r="AA7">
-        <v>-1.298119964189794</v>
-      </c>
-      <c r="AB7">
-        <v>0.05655198227056123</v>
-      </c>
-      <c r="AC7">
-        <v>-1.354671946460356</v>
-      </c>
-      <c r="AD7">
-        <v>1.02</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>1.02</v>
-      </c>
-      <c r="AG7">
-        <v>-31.58</v>
-      </c>
-      <c r="AH7">
-        <v>0.008541282867191425</v>
-      </c>
-      <c r="AI7">
-        <v>0.009548773637895526</v>
-      </c>
-      <c r="AJ7">
-        <v>-0.363741073485372</v>
-      </c>
-      <c r="AK7">
-        <v>-0.4254917811910536</v>
-      </c>
-      <c r="AL7">
-        <v>0.375</v>
-      </c>
-      <c r="AM7">
-        <v>-5.015</v>
-      </c>
-      <c r="AN7">
-        <v>-0.07391304347826087</v>
-      </c>
-      <c r="AO7">
-        <v>-38.66666666666666</v>
-      </c>
-      <c r="AP7">
-        <v>2.288405797101449</v>
-      </c>
-      <c r="AQ7">
-        <v>2.891326021934197</v>
+      <c r="G11">
+        <v>-1.398230088495575</v>
+      </c>
+      <c r="H11">
+        <v>-1.398230088495575</v>
+      </c>
+      <c r="I11">
+        <v>-1.371681415929203</v>
+      </c>
+      <c r="J11">
+        <v>-1.371681415929203</v>
+      </c>
+      <c r="K11">
+        <v>-18.9</v>
+      </c>
+      <c r="L11">
+        <v>-1.672566371681416</v>
+      </c>
+      <c r="M11">
+        <v>0.279</v>
+      </c>
+      <c r="N11">
+        <v>0.00554671968190855</v>
+      </c>
+      <c r="O11">
+        <v>-0.01476190476190476</v>
+      </c>
+      <c r="P11">
+        <v>0.279</v>
+      </c>
+      <c r="Q11">
+        <v>0.00554671968190855</v>
+      </c>
+      <c r="R11">
+        <v>-0.01476190476190476</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>18.8</v>
+      </c>
+      <c r="V11">
+        <v>0.3737574552683897</v>
+      </c>
+      <c r="W11">
+        <v>-0.1789772727272727</v>
+      </c>
+      <c r="X11">
+        <v>0.06042140442969166</v>
+      </c>
+      <c r="Y11">
+        <v>-0.2393986771569644</v>
+      </c>
+      <c r="Z11">
+        <v>0.1981760785689232</v>
+      </c>
+      <c r="AA11">
+        <v>-0.2718344440547177</v>
+      </c>
+      <c r="AB11">
+        <v>0.06042774576383177</v>
+      </c>
+      <c r="AC11">
+        <v>-0.3322621898185495</v>
+      </c>
+      <c r="AD11">
+        <v>0.23</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0.23</v>
+      </c>
+      <c r="AG11">
+        <v>-18.57</v>
+      </c>
+      <c r="AH11">
+        <v>0.004551751434791214</v>
+      </c>
+      <c r="AI11">
+        <v>0.002400083481164563</v>
+      </c>
+      <c r="AJ11">
+        <v>-0.585250551528522</v>
+      </c>
+      <c r="AK11">
+        <v>-0.2410749058808256</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>-3.96</v>
+      </c>
+      <c r="AN11">
+        <v>-0.01513157894736842</v>
+      </c>
+      <c r="AP11">
+        <v>1.221710526315789</v>
+      </c>
+      <c r="AQ11">
+        <v>3.914141414141414</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/brazil/brazil_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,109 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.114</v>
+        <v>0.11</v>
       </c>
       <c r="E2">
-        <v>0.09050000000000001</v>
+        <v>0.1023</v>
+      </c>
+      <c r="F2">
+        <v>0.09285</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.3833465516950439</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.349794412289139</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.2968787791858614</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.2326058077690838</v>
       </c>
       <c r="K2">
-        <v>392.9</v>
+        <v>1526.2</v>
       </c>
       <c r="L2">
-        <v>0.191780153267926</v>
+        <v>0.2146155706676117</v>
       </c>
       <c r="M2">
-        <v>94.7</v>
+        <v>1166.958</v>
       </c>
       <c r="N2">
-        <v>0.05856524427953</v>
+        <v>0.09175857269789349</v>
       </c>
       <c r="O2">
-        <v>0.2410282514634767</v>
+        <v>0.7646166950596252</v>
       </c>
       <c r="P2">
-        <v>94.7</v>
+        <v>493.19</v>
       </c>
       <c r="Q2">
-        <v>0.05856524427953</v>
+        <v>0.0387798108148486</v>
       </c>
       <c r="R2">
-        <v>0.2410282514634767</v>
+        <v>0.3231489975101559</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>673.7679999999999</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.5773712507219626</v>
       </c>
       <c r="U2">
-        <v>24.3</v>
+        <v>529.9399999999999</v>
       </c>
       <c r="V2">
-        <v>0.0150278293135436</v>
+        <v>0.04166948426209142</v>
       </c>
       <c r="W2">
         <v>0.1911178130168304</v>
       </c>
       <c r="X2">
-        <v>0.08044247718706449</v>
+        <v>0.06751023269147713</v>
       </c>
       <c r="Y2">
-        <v>0.1106753358297659</v>
+        <v>0.1236075803253533</v>
       </c>
       <c r="Z2">
-        <v>0.5008311739109176</v>
+        <v>0.9651314289436825</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>0.22604882763351</v>
       </c>
       <c r="AB2">
-        <v>0.06797154092705536</v>
+        <v>0.06434815954145653</v>
       </c>
       <c r="AC2">
-        <v>-0.06797154092705536</v>
+        <v>0.1617719977415878</v>
       </c>
       <c r="AD2">
-        <v>2168</v>
+        <v>5221.94</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2168</v>
+        <v>5221.94</v>
       </c>
       <c r="AG2">
-        <v>2143.7</v>
+        <v>4692</v>
       </c>
       <c r="AH2">
-        <v>0.5727873183619551</v>
+        <v>0.2910838790521995</v>
       </c>
       <c r="AI2">
-        <v>0.4654158258554807</v>
+        <v>0.372728414765411</v>
       </c>
       <c r="AJ2">
-        <v>0.5700268567022096</v>
+        <v>0.2695049311590665</v>
       </c>
       <c r="AK2">
-        <v>0.4626124862426897</v>
+        <v>0.3480686345056787</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>784.2529999999999</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>504.05</v>
+      </c>
+      <c r="AN2">
+        <v>2.282615727586659</v>
+      </c>
+      <c r="AO2">
+        <v>2.691988427203976</v>
+      </c>
+      <c r="AP2">
+        <v>2.050968221357696</v>
+      </c>
+      <c r="AQ2">
+        <v>4.188473365737526</v>
       </c>
     </row>
     <row r="3">
@@ -701,118 +716,654 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>B3 S.A. - Brasil, Bolsa, Balcão (BOVESPA:B3SA3)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>0.106</v>
+      </c>
+      <c r="E3">
+        <v>0.11</v>
+      </c>
+      <c r="F3">
+        <v>0.04769999999999999</v>
+      </c>
+      <c r="G3">
+        <v>0.7889192806843973</v>
+      </c>
+      <c r="H3">
+        <v>0.6500611069079905</v>
+      </c>
+      <c r="I3">
+        <v>0.62433800849677</v>
+      </c>
+      <c r="J3">
+        <v>0.4618119237452299</v>
+      </c>
+      <c r="K3">
+        <v>792.2</v>
+      </c>
+      <c r="L3">
+        <v>0.4610370715241809</v>
+      </c>
+      <c r="M3">
+        <v>957.6999999999999</v>
+      </c>
+      <c r="N3">
+        <v>0.1064063819385805</v>
+      </c>
+      <c r="O3">
+        <v>1.208911890936632</v>
+      </c>
+      <c r="P3">
+        <v>390.9</v>
+      </c>
+      <c r="Q3">
+        <v>0.04343140304875339</v>
+      </c>
+      <c r="R3">
+        <v>0.4934360010098459</v>
+      </c>
+      <c r="S3">
+        <v>566.8</v>
+      </c>
+      <c r="T3">
+        <v>0.5918346037381226</v>
+      </c>
+      <c r="U3">
+        <v>349.2</v>
+      </c>
+      <c r="V3">
+        <v>0.03879827563219412</v>
+      </c>
+      <c r="W3">
+        <v>0.1955325188201901</v>
+      </c>
+      <c r="X3">
+        <v>0.06751023269147713</v>
+      </c>
+      <c r="Y3">
+        <v>0.1280222861287129</v>
+      </c>
+      <c r="Z3">
+        <v>1.823129973474801</v>
+      </c>
+      <c r="AA3">
+        <v>0.8419431602879879</v>
+      </c>
+      <c r="AB3">
+        <v>0.06385365302129495</v>
+      </c>
+      <c r="AC3">
+        <v>0.7780895072666929</v>
+      </c>
+      <c r="AD3">
+        <v>2474.2</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>2474.2</v>
+      </c>
+      <c r="AG3">
+        <v>2125</v>
+      </c>
+      <c r="AH3">
+        <v>0.2156240740417967</v>
+      </c>
+      <c r="AI3">
+        <v>0.4128827701293283</v>
+      </c>
+      <c r="AJ3">
+        <v>0.1910043683822604</v>
+      </c>
+      <c r="AK3">
+        <v>0.376552726241738</v>
+      </c>
+      <c r="AL3">
+        <v>247.6</v>
+      </c>
+      <c r="AM3">
+        <v>-30.40000000000001</v>
+      </c>
+      <c r="AN3">
+        <v>2.542334566378956</v>
+      </c>
+      <c r="AO3">
+        <v>4.332794830371567</v>
+      </c>
+      <c r="AP3">
+        <v>2.183518290176736</v>
+      </c>
+      <c r="AQ3">
+        <v>-35.28947368421052</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PagSeguro Digital Ltd. (NYSE:PAGS)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.275</v>
+      </c>
+      <c r="E4">
+        <v>0.0946</v>
+      </c>
+      <c r="F4">
+        <v>0.138</v>
+      </c>
+      <c r="G4">
+        <v>0.4285184039591711</v>
+      </c>
+      <c r="H4">
+        <v>0.4285184039591711</v>
+      </c>
+      <c r="I4">
+        <v>0.3255799566965666</v>
+      </c>
+      <c r="J4">
+        <v>0.280559424546901</v>
+      </c>
+      <c r="K4">
+        <v>368.3</v>
+      </c>
+      <c r="L4">
+        <v>0.1139189607175998</v>
+      </c>
+      <c r="M4">
+        <v>106.2</v>
+      </c>
+      <c r="N4">
+        <v>0.0543778801843318</v>
+      </c>
+      <c r="O4">
+        <v>0.2883518870486017</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>-0</v>
+      </c>
+      <c r="S4">
+        <v>106.2</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
+      <c r="U4">
+        <v>132.2</v>
+      </c>
+      <c r="V4">
+        <v>0.06769073220686124</v>
+      </c>
+      <c r="W4">
+        <v>0.1429347615166686</v>
+      </c>
+      <c r="X4">
+        <v>0.06768301231355581</v>
+      </c>
+      <c r="Y4">
+        <v>0.07525174920311281</v>
+      </c>
+      <c r="Z4">
+        <v>1.468477470930233</v>
+      </c>
+      <c r="AA4">
+        <v>0.4119951942042747</v>
+      </c>
+      <c r="AB4">
+        <v>0.06435880213175216</v>
+      </c>
+      <c r="AC4">
+        <v>0.3476363920725226</v>
+      </c>
+      <c r="AD4">
+        <v>564.7</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>564.7</v>
+      </c>
+      <c r="AG4">
+        <v>432.5000000000001</v>
+      </c>
+      <c r="AH4">
+        <v>0.224292012551138</v>
+      </c>
+      <c r="AI4">
+        <v>0.1755307575145317</v>
+      </c>
+      <c r="AJ4">
+        <v>0.1813037099140642</v>
+      </c>
+      <c r="AK4">
+        <v>0.1401990340043437</v>
+      </c>
+      <c r="AL4">
+        <v>534.9</v>
+      </c>
+      <c r="AM4">
+        <v>534.9</v>
+      </c>
+      <c r="AN4">
+        <v>0.4246503233568958</v>
+      </c>
+      <c r="AO4">
+        <v>1.967844456907833</v>
+      </c>
+      <c r="AP4">
+        <v>0.3252368777259739</v>
+      </c>
+      <c r="AQ4">
+        <v>1.967844456907833</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CSU Digital S.A. (BOVESPA:CSUD3)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.0601</v>
+      </c>
+      <c r="E5">
+        <v>0.286</v>
+      </c>
+      <c r="G5">
+        <v>0.2451171875</v>
+      </c>
+      <c r="H5">
+        <v>0.2451171875</v>
+      </c>
+      <c r="I5">
+        <v>0.232421875</v>
+      </c>
+      <c r="J5">
+        <v>0.1680134401483051</v>
+      </c>
+      <c r="K5">
+        <v>17.1</v>
+      </c>
+      <c r="L5">
+        <v>0.1669921875</v>
+      </c>
+      <c r="M5">
+        <v>7.59</v>
+      </c>
+      <c r="N5">
+        <v>0.07383268482490273</v>
+      </c>
+      <c r="O5">
+        <v>0.443859649122807</v>
+      </c>
+      <c r="P5">
+        <v>7.59</v>
+      </c>
+      <c r="Q5">
+        <v>0.07383268482490273</v>
+      </c>
+      <c r="R5">
+        <v>0.443859649122807</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>14.9</v>
+      </c>
+      <c r="V5">
+        <v>0.1449416342412451</v>
+      </c>
+      <c r="W5">
+        <v>0.2070217917675545</v>
+      </c>
+      <c r="X5">
+        <v>0.0658868829044346</v>
+      </c>
+      <c r="Y5">
+        <v>0.1411349088631199</v>
+      </c>
+      <c r="Z5">
+        <v>1.345421101037972</v>
+      </c>
+      <c r="AA5">
+        <v>0.22604882763351</v>
+      </c>
+      <c r="AB5">
+        <v>0.06427682989192214</v>
+      </c>
+      <c r="AC5">
+        <v>0.1617719977415878</v>
+      </c>
+      <c r="AD5">
+        <v>14.5</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>14.5</v>
+      </c>
+      <c r="AG5">
+        <v>-0.4000000000000004</v>
+      </c>
+      <c r="AH5">
+        <v>0.123614663256607</v>
+      </c>
+      <c r="AI5">
+        <v>0.1461693548387097</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.003906250000000003</v>
+      </c>
+      <c r="AK5">
+        <v>-0.004744958481613291</v>
+      </c>
+      <c r="AL5">
+        <v>1.61</v>
+      </c>
+      <c r="AM5">
+        <v>0.3500000000000001</v>
+      </c>
+      <c r="AN5">
+        <v>0.6016597510373444</v>
+      </c>
+      <c r="AO5">
+        <v>14.78260869565217</v>
+      </c>
+      <c r="AP5">
+        <v>-0.016597510373444</v>
+      </c>
+      <c r="AQ5">
+        <v>67.99999999999999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Banco do Nordeste do Brasil S.A. (BOVESPA:BNBR3)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="D6">
         <v>0.114</v>
       </c>
-      <c r="E3">
+      <c r="E6">
         <v>0.09050000000000001</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
         <v>392.9</v>
       </c>
-      <c r="L3">
+      <c r="L6">
         <v>0.191780153267926</v>
       </c>
-      <c r="M3">
+      <c r="M6">
         <v>94.7</v>
       </c>
-      <c r="N3">
+      <c r="N6">
         <v>0.05856524427953</v>
       </c>
-      <c r="O3">
+      <c r="O6">
         <v>0.2410282514634767</v>
       </c>
-      <c r="P3">
+      <c r="P6">
         <v>94.7</v>
       </c>
-      <c r="Q3">
+      <c r="Q6">
         <v>0.05856524427953</v>
       </c>
-      <c r="R3">
+      <c r="R6">
         <v>0.2410282514634767</v>
       </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
         <v>24.3</v>
       </c>
-      <c r="V3">
+      <c r="V6">
         <v>0.0150278293135436</v>
       </c>
-      <c r="W3">
+      <c r="W6">
         <v>0.1911178130168304</v>
       </c>
-      <c r="X3">
-        <v>0.08044247718706449</v>
-      </c>
-      <c r="Y3">
-        <v>0.1106753358297659</v>
-      </c>
-      <c r="Z3">
+      <c r="X6">
+        <v>0.08043722780237808</v>
+      </c>
+      <c r="Y6">
+        <v>0.1106805852144523</v>
+      </c>
+      <c r="Z6">
         <v>0.5008311739109176</v>
       </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0.06797154092705536</v>
-      </c>
-      <c r="AC3">
-        <v>-0.06797154092705536</v>
-      </c>
-      <c r="AD3">
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.06796929832334653</v>
+      </c>
+      <c r="AC6">
+        <v>-0.06796929832334653</v>
+      </c>
+      <c r="AD6">
         <v>2168</v>
       </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
         <v>2168</v>
       </c>
-      <c r="AG3">
+      <c r="AG6">
         <v>2143.7</v>
       </c>
-      <c r="AH3">
+      <c r="AH6">
         <v>0.5727873183619551</v>
       </c>
-      <c r="AI3">
+      <c r="AI6">
         <v>0.4654158258554807</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ6">
         <v>0.5700268567022096</v>
       </c>
-      <c r="AK3">
+      <c r="AK6">
         <v>0.4626124862426897</v>
       </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TC S.A. (BOVESPA:TRAD3)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G7">
+        <v>-4.484304932735426</v>
+      </c>
+      <c r="H7">
+        <v>-4.484304932735426</v>
+      </c>
+      <c r="I7">
+        <v>-4.260089686098655</v>
+      </c>
+      <c r="J7">
+        <v>-4.260089686098655</v>
+      </c>
+      <c r="K7">
+        <v>-44.3</v>
+      </c>
+      <c r="L7">
+        <v>-4.966367713004484</v>
+      </c>
+      <c r="M7">
+        <v>0.768</v>
+      </c>
+      <c r="N7">
+        <v>0.01725842696629214</v>
+      </c>
+      <c r="O7">
+        <v>-0.01733634311512415</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0.768</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>9.34</v>
+      </c>
+      <c r="V7">
+        <v>0.2098876404494382</v>
+      </c>
+      <c r="W7">
+        <v>-0.4638743455497382</v>
+      </c>
+      <c r="X7">
+        <v>0.06432335655654596</v>
+      </c>
+      <c r="Y7">
+        <v>-0.5281977021062841</v>
+      </c>
+      <c r="Z7">
+        <v>0.1553195194149399</v>
+      </c>
+      <c r="AA7">
+        <v>-0.6616750827093852</v>
+      </c>
+      <c r="AB7">
+        <v>0.06434815954145653</v>
+      </c>
+      <c r="AC7">
+        <v>-0.7260232422508418</v>
+      </c>
+      <c r="AD7">
+        <v>0.54</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0.54</v>
+      </c>
+      <c r="AG7">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="AH7">
+        <v>0.01198934280639432</v>
+      </c>
+      <c r="AI7">
+        <v>0.01254646840148699</v>
+      </c>
+      <c r="AJ7">
+        <v>-0.2464985994397759</v>
+      </c>
+      <c r="AK7">
+        <v>-0.2611275964391692</v>
+      </c>
+      <c r="AL7">
+        <v>0.143</v>
+      </c>
+      <c r="AM7">
+        <v>-0.7999999999999999</v>
+      </c>
+      <c r="AN7">
+        <v>-0.01370558375634518</v>
+      </c>
+      <c r="AO7">
+        <v>-265.7342657342658</v>
+      </c>
+      <c r="AP7">
+        <v>0.2233502538071066</v>
+      </c>
+      <c r="AQ7">
+        <v>47.50000000000001</v>
       </c>
     </row>
   </sheetData>
